--- a/formlar/16. Organik Üretim/EMS.OR.FRM.21.07. Organik Sevkiyat ve TC Talep Formu.xlsx
+++ b/formlar/16. Organik Üretim/EMS.OR.FRM.21.07. Organik Sevkiyat ve TC Talep Formu.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Form" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,8 +67,37 @@
       <name val="Calibri"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="25"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -90,8 +119,18 @@
         <fgColor rgb="00F6F7F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00006600"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF1DE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -182,11 +221,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <top style="medium"/>
+    </border>
+    <border>
+      <top style="medium"/>
+    </border>
+    <border>
+      <left style="medium"/>
+    </border>
+    <border/>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -239,6 +319,47 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -316,32 +437,67 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
-      <colOff>0</colOff>
+      <colOff>238124</colOff>
       <row>0</row>
-      <rowOff>0</rowOff>
+      <rowOff>198193</rowOff>
     </from>
-    <ext cx="1219200" cy="952500"/>
+    <to>
+      <col>2</col>
+      <colOff>171449</colOff>
+      <row>3</row>
+      <rowOff>205802</rowOff>
+    </to>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>15</col>
+      <colOff>66676</colOff>
+      <row>0</row>
+      <rowOff>28575</rowOff>
+    </from>
+    <to>
+      <col>16</col>
+      <colOff>609600</colOff>
+      <row>3</row>
+      <rowOff>283176</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
 </wsDr>
 </file>
 
@@ -660,584 +816,587 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="A1" s="24" t="n"/>
+      <c r="B1" s="25" t="n"/>
+      <c r="C1" s="26" t="n"/>
+      <c r="D1" s="27" t="inlineStr">
         <is>
           <t>ORGANIC SHIPMENT AND TC REQUEST FORM
 نموذج الشحن العضوي وطلب شهادة المعاملة</t>
         </is>
       </c>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
-      <c r="N1" s="1" t="n"/>
-      <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="n"/>
-      <c r="Q1" s="1" t="n"/>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="E1" s="25" t="n"/>
+      <c r="F1" s="25" t="n"/>
+      <c r="G1" s="25" t="n"/>
+      <c r="H1" s="25" t="n"/>
+      <c r="I1" s="25" t="n"/>
+      <c r="J1" s="25" t="n"/>
+      <c r="K1" s="25" t="n"/>
+      <c r="L1" s="25" t="n"/>
+      <c r="M1" s="25" t="n"/>
+      <c r="N1" s="25" t="n"/>
+      <c r="O1" s="25" t="n"/>
+      <c r="P1" s="25" t="n"/>
+      <c r="Q1" s="25" t="n"/>
+      <c r="R1" s="28" t="inlineStr">
         <is>
           <t>DATE / التاريخ</t>
         </is>
       </c>
-      <c r="S1" s="5" t="n"/>
-      <c r="T1" s="6" t="inlineStr">
+      <c r="S1" s="29" t="n"/>
+      <c r="T1" s="30" t="inlineStr">
         <is>
           <t>….../….../.…</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="7" t="n"/>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
-      <c r="H2" s="1" t="n"/>
-      <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="n"/>
-      <c r="K2" s="1" t="n"/>
-      <c r="L2" s="1" t="n"/>
-      <c r="M2" s="1" t="n"/>
-      <c r="N2" s="1" t="n"/>
-      <c r="O2" s="1" t="n"/>
-      <c r="P2" s="1" t="n"/>
-      <c r="Q2" s="1" t="n"/>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="A2" s="31" t="n"/>
+      <c r="B2" s="32" t="n"/>
+      <c r="C2" s="32" t="n"/>
+      <c r="D2" s="32" t="n"/>
+      <c r="E2" s="32" t="n"/>
+      <c r="F2" s="32" t="n"/>
+      <c r="G2" s="32" t="n"/>
+      <c r="H2" s="32" t="n"/>
+      <c r="I2" s="32" t="n"/>
+      <c r="J2" s="32" t="n"/>
+      <c r="K2" s="32" t="n"/>
+      <c r="L2" s="32" t="n"/>
+      <c r="M2" s="32" t="n"/>
+      <c r="N2" s="32" t="n"/>
+      <c r="O2" s="32" t="n"/>
+      <c r="P2" s="32" t="n"/>
+      <c r="Q2" s="32" t="n"/>
+      <c r="R2" s="28" t="inlineStr">
         <is>
           <t>FORM NUMBER / رقم النموذج</t>
         </is>
       </c>
-      <c r="S2" s="5" t="n"/>
-      <c r="T2" s="9" t="inlineStr">
+      <c r="S2" s="29" t="n"/>
+      <c r="T2" s="33" t="inlineStr">
         <is>
           <t>EMS.OR.FRM.21.07</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="8" t="n"/>
-      <c r="C3" s="1" t="n"/>
-      <c r="D3" s="1" t="n"/>
-      <c r="E3" s="1" t="n"/>
-      <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
-      <c r="H3" s="1" t="n"/>
-      <c r="I3" s="1" t="n"/>
-      <c r="J3" s="1" t="n"/>
-      <c r="K3" s="1" t="n"/>
-      <c r="L3" s="1" t="n"/>
-      <c r="M3" s="1" t="n"/>
-      <c r="N3" s="1" t="n"/>
-      <c r="O3" s="1" t="n"/>
-      <c r="P3" s="1" t="n"/>
-      <c r="Q3" s="1" t="n"/>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="A3" s="31" t="n"/>
+      <c r="B3" s="32" t="n"/>
+      <c r="C3" s="32" t="n"/>
+      <c r="D3" s="32" t="n"/>
+      <c r="E3" s="32" t="n"/>
+      <c r="F3" s="32" t="n"/>
+      <c r="G3" s="32" t="n"/>
+      <c r="H3" s="32" t="n"/>
+      <c r="I3" s="32" t="n"/>
+      <c r="J3" s="32" t="n"/>
+      <c r="K3" s="32" t="n"/>
+      <c r="L3" s="32" t="n"/>
+      <c r="M3" s="32" t="n"/>
+      <c r="N3" s="32" t="n"/>
+      <c r="O3" s="32" t="n"/>
+      <c r="P3" s="32" t="n"/>
+      <c r="Q3" s="32" t="n"/>
+      <c r="R3" s="28" t="inlineStr">
         <is>
           <t>REVISION / المراجعة</t>
         </is>
       </c>
-      <c r="S3" s="5" t="n"/>
-      <c r="T3" s="6" t="inlineStr">
+      <c r="S3" s="29" t="n"/>
+      <c r="T3" s="30" t="inlineStr">
         <is>
           <t>R00</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="10" t="n"/>
-      <c r="B4" s="11" t="n"/>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-      <c r="E4" s="1" t="n"/>
-      <c r="F4" s="1" t="n"/>
-      <c r="G4" s="1" t="n"/>
-      <c r="H4" s="1" t="n"/>
-      <c r="I4" s="1" t="n"/>
-      <c r="J4" s="1" t="n"/>
-      <c r="K4" s="1" t="n"/>
-      <c r="L4" s="1" t="n"/>
-      <c r="M4" s="1" t="n"/>
-      <c r="N4" s="1" t="n"/>
-      <c r="O4" s="1" t="n"/>
-      <c r="P4" s="1" t="n"/>
-      <c r="Q4" s="1" t="n"/>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="A4" s="31" t="n"/>
+      <c r="B4" s="32" t="n"/>
+      <c r="C4" s="32" t="n"/>
+      <c r="D4" s="32" t="n"/>
+      <c r="E4" s="32" t="n"/>
+      <c r="F4" s="32" t="n"/>
+      <c r="G4" s="32" t="n"/>
+      <c r="H4" s="32" t="n"/>
+      <c r="I4" s="32" t="n"/>
+      <c r="J4" s="32" t="n"/>
+      <c r="K4" s="32" t="n"/>
+      <c r="L4" s="32" t="n"/>
+      <c r="M4" s="32" t="n"/>
+      <c r="N4" s="32" t="n"/>
+      <c r="O4" s="32" t="n"/>
+      <c r="P4" s="32" t="n"/>
+      <c r="Q4" s="32" t="n"/>
+      <c r="R4" s="28" t="inlineStr">
         <is>
           <t>PUBLIC. DATE / تاريخ النشر</t>
         </is>
       </c>
-      <c r="S4" s="5" t="n"/>
-      <c r="T4" s="6" t="inlineStr">
+      <c r="S4" s="29" t="n"/>
+      <c r="T4" s="30" t="inlineStr">
         <is>
           <t>19.10.2026</t>
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>GENERAL INFORMATION / المعلومات العامة</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="13" t="n"/>
-      <c r="H6" s="13" t="n"/>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="13" t="n"/>
-      <c r="K6" s="13" t="n"/>
-      <c r="L6" s="13" t="n"/>
-      <c r="M6" s="13" t="n"/>
-      <c r="N6" s="13" t="n"/>
-      <c r="O6" s="13" t="n"/>
-      <c r="P6" s="13" t="n"/>
-      <c r="Q6" s="13" t="n"/>
-      <c r="R6" s="13" t="n"/>
-      <c r="S6" s="13" t="n"/>
-      <c r="T6" s="13" t="n"/>
+      <c r="B6" s="35" t="n"/>
+      <c r="C6" s="35" t="n"/>
+      <c r="D6" s="35" t="n"/>
+      <c r="E6" s="35" t="n"/>
+      <c r="F6" s="35" t="n"/>
+      <c r="G6" s="35" t="n"/>
+      <c r="H6" s="35" t="n"/>
+      <c r="I6" s="35" t="n"/>
+      <c r="J6" s="35" t="n"/>
+      <c r="K6" s="35" t="n"/>
+      <c r="L6" s="35" t="n"/>
+      <c r="M6" s="35" t="n"/>
+      <c r="N6" s="35" t="n"/>
+      <c r="O6" s="35" t="n"/>
+      <c r="P6" s="35" t="n"/>
+      <c r="Q6" s="35" t="n"/>
+      <c r="R6" s="35" t="n"/>
+      <c r="S6" s="35" t="n"/>
+      <c r="T6" s="36" t="n"/>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>Customer
 العميل</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n"/>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="15" t="n"/>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="B7" s="35" t="n"/>
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="35" t="n"/>
+      <c r="E7" s="35" t="n"/>
+      <c r="F7" s="36" t="n"/>
+      <c r="G7" s="37" t="inlineStr">
         <is>
           <t>Invoice No
 رقم الفاتورة</t>
         </is>
       </c>
-      <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="n"/>
-      <c r="K7" s="14" t="inlineStr">
+      <c r="H7" s="35" t="n"/>
+      <c r="I7" s="35" t="n"/>
+      <c r="J7" s="36" t="n"/>
+      <c r="K7" s="37" t="inlineStr">
         <is>
           <t>Packing list No
 رقم قائمة التعبئة</t>
         </is>
       </c>
-      <c r="L7" s="15" t="n"/>
-      <c r="M7" s="15" t="n"/>
-      <c r="N7" s="15" t="n"/>
-      <c r="O7" s="15" t="n"/>
-      <c r="P7" s="14" t="inlineStr">
+      <c r="L7" s="35" t="n"/>
+      <c r="M7" s="35" t="n"/>
+      <c r="N7" s="35" t="n"/>
+      <c r="O7" s="36" t="n"/>
+      <c r="P7" s="37" t="inlineStr">
         <is>
           <t>Shipment date
 تاريخ الشحن</t>
         </is>
       </c>
-      <c r="Q7" s="15" t="n"/>
-      <c r="R7" s="15" t="n"/>
-      <c r="S7" s="15" t="n"/>
-      <c r="T7" s="15" t="n"/>
+      <c r="Q7" s="35" t="n"/>
+      <c r="R7" s="35" t="n"/>
+      <c r="S7" s="35" t="n"/>
+      <c r="T7" s="36" t="n"/>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Vehicle / container No
 رقم المركبة / الحاوية</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="15" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="B8" s="35" t="n"/>
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="35" t="n"/>
+      <c r="E8" s="35" t="n"/>
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="37" t="inlineStr">
         <is>
           <t>Standard  ☐ GOTS  ☐ OCS
 المعيار</t>
         </is>
       </c>
-      <c r="H8" s="15" t="n"/>
-      <c r="I8" s="15" t="n"/>
-      <c r="J8" s="15" t="n"/>
-      <c r="K8" s="15" t="n"/>
-      <c r="L8" s="15" t="n"/>
-      <c r="M8" s="14" t="inlineStr">
+      <c r="H8" s="35" t="n"/>
+      <c r="I8" s="35" t="n"/>
+      <c r="J8" s="35" t="n"/>
+      <c r="K8" s="35" t="n"/>
+      <c r="L8" s="36" t="n"/>
+      <c r="M8" s="37" t="inlineStr">
         <is>
           <t>Prepared by
 المعد</t>
         </is>
       </c>
-      <c r="N8" s="15" t="n"/>
-      <c r="O8" s="15" t="n"/>
-      <c r="P8" s="15" t="n"/>
-      <c r="Q8" s="15" t="n"/>
-      <c r="R8" s="15" t="n"/>
-      <c r="S8" s="15" t="n"/>
-      <c r="T8" s="15" t="n"/>
-    </row>
+      <c r="N8" s="35" t="n"/>
+      <c r="O8" s="35" t="n"/>
+      <c r="P8" s="35" t="n"/>
+      <c r="Q8" s="35" t="n"/>
+      <c r="R8" s="35" t="n"/>
+      <c r="S8" s="35" t="n"/>
+      <c r="T8" s="36" t="n"/>
+    </row>
+    <row r="9"/>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>SHIPPED GOODS / البضائع المشحونة</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="13" t="n"/>
-      <c r="J10" s="13" t="n"/>
-      <c r="K10" s="13" t="n"/>
-      <c r="L10" s="13" t="n"/>
-      <c r="M10" s="13" t="n"/>
-      <c r="N10" s="13" t="n"/>
-      <c r="O10" s="13" t="n"/>
-      <c r="P10" s="13" t="n"/>
-      <c r="Q10" s="13" t="n"/>
-      <c r="R10" s="13" t="n"/>
-      <c r="S10" s="13" t="n"/>
-      <c r="T10" s="13" t="n"/>
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n"/>
+      <c r="F10" s="35" t="n"/>
+      <c r="G10" s="35" t="n"/>
+      <c r="H10" s="35" t="n"/>
+      <c r="I10" s="35" t="n"/>
+      <c r="J10" s="35" t="n"/>
+      <c r="K10" s="35" t="n"/>
+      <c r="L10" s="35" t="n"/>
+      <c r="M10" s="35" t="n"/>
+      <c r="N10" s="35" t="n"/>
+      <c r="O10" s="35" t="n"/>
+      <c r="P10" s="35" t="n"/>
+      <c r="Q10" s="35" t="n"/>
+      <c r="R10" s="35" t="n"/>
+      <c r="S10" s="35" t="n"/>
+      <c r="T10" s="36" t="n"/>
     </row>
     <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
         <is>
           <t>Order / PO No
 رقم الطلب</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="38" t="inlineStr">
         <is>
           <t>Product / style
 المنتج / الموديل</t>
         </is>
       </c>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="F11" s="35" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="38" t="inlineStr">
         <is>
           <t>Organic lot No
 رقم الدفعة العضوية</t>
         </is>
       </c>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="16" t="inlineStr">
+      <c r="I11" s="35" t="n"/>
+      <c r="J11" s="36" t="n"/>
+      <c r="K11" s="38" t="inlineStr">
         <is>
           <t>Qty (pcs)
 الكمية</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="16" t="inlineStr">
+      <c r="L11" s="36" t="n"/>
+      <c r="M11" s="38" t="inlineStr">
         <is>
           <t>Cartons
 الكراتين</t>
         </is>
       </c>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="16" t="inlineStr">
+      <c r="N11" s="36" t="n"/>
+      <c r="O11" s="38" t="inlineStr">
         <is>
           <t>Claim wording on documents
 عبارة الادعاء في الوثائق</t>
         </is>
       </c>
-      <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="5" t="n"/>
-      <c r="R11" s="16" t="inlineStr">
+      <c r="P11" s="35" t="n"/>
+      <c r="Q11" s="36" t="n"/>
+      <c r="R11" s="38" t="inlineStr">
         <is>
           <t>Label / docs OK
 الملصق / الوثائق سليمة</t>
         </is>
       </c>
-      <c r="S11" s="5" t="n"/>
-      <c r="T11" s="5" t="n"/>
+      <c r="S11" s="35" t="n"/>
+      <c r="T11" s="36" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="17" t="n">
         <v>1</v>
       </c>
       <c r="B12" s="17" t="n"/>
-      <c r="C12" s="1" t="n"/>
-      <c r="D12" s="1" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="36" t="n"/>
       <c r="E12" s="17" t="n"/>
-      <c r="F12" s="1" t="n"/>
-      <c r="G12" s="1" t="n"/>
+      <c r="F12" s="35" t="n"/>
+      <c r="G12" s="36" t="n"/>
       <c r="H12" s="17" t="n"/>
-      <c r="I12" s="1" t="n"/>
-      <c r="J12" s="1" t="n"/>
+      <c r="I12" s="35" t="n"/>
+      <c r="J12" s="36" t="n"/>
       <c r="K12" s="17" t="n"/>
-      <c r="L12" s="1" t="n"/>
+      <c r="L12" s="36" t="n"/>
       <c r="M12" s="17" t="n"/>
-      <c r="N12" s="1" t="n"/>
+      <c r="N12" s="36" t="n"/>
       <c r="O12" s="17" t="n"/>
-      <c r="P12" s="1" t="n"/>
-      <c r="Q12" s="1" t="n"/>
+      <c r="P12" s="35" t="n"/>
+      <c r="Q12" s="36" t="n"/>
       <c r="R12" s="17" t="n"/>
-      <c r="S12" s="1" t="n"/>
-      <c r="T12" s="1" t="n"/>
+      <c r="S12" s="35" t="n"/>
+      <c r="T12" s="36" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="17" t="n">
         <v>2</v>
       </c>
       <c r="B13" s="17" t="n"/>
-      <c r="C13" s="1" t="n"/>
-      <c r="D13" s="1" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="36" t="n"/>
       <c r="E13" s="17" t="n"/>
-      <c r="F13" s="1" t="n"/>
-      <c r="G13" s="1" t="n"/>
+      <c r="F13" s="35" t="n"/>
+      <c r="G13" s="36" t="n"/>
       <c r="H13" s="17" t="n"/>
-      <c r="I13" s="1" t="n"/>
-      <c r="J13" s="1" t="n"/>
+      <c r="I13" s="35" t="n"/>
+      <c r="J13" s="36" t="n"/>
       <c r="K13" s="17" t="n"/>
-      <c r="L13" s="1" t="n"/>
+      <c r="L13" s="36" t="n"/>
       <c r="M13" s="17" t="n"/>
-      <c r="N13" s="1" t="n"/>
+      <c r="N13" s="36" t="n"/>
       <c r="O13" s="17" t="n"/>
-      <c r="P13" s="1" t="n"/>
-      <c r="Q13" s="1" t="n"/>
+      <c r="P13" s="35" t="n"/>
+      <c r="Q13" s="36" t="n"/>
       <c r="R13" s="17" t="n"/>
-      <c r="S13" s="1" t="n"/>
-      <c r="T13" s="1" t="n"/>
+      <c r="S13" s="35" t="n"/>
+      <c r="T13" s="36" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="17" t="n">
         <v>3</v>
       </c>
       <c r="B14" s="17" t="n"/>
-      <c r="C14" s="1" t="n"/>
-      <c r="D14" s="1" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="36" t="n"/>
       <c r="E14" s="17" t="n"/>
-      <c r="F14" s="1" t="n"/>
-      <c r="G14" s="1" t="n"/>
+      <c r="F14" s="35" t="n"/>
+      <c r="G14" s="36" t="n"/>
       <c r="H14" s="17" t="n"/>
-      <c r="I14" s="1" t="n"/>
-      <c r="J14" s="1" t="n"/>
+      <c r="I14" s="35" t="n"/>
+      <c r="J14" s="36" t="n"/>
       <c r="K14" s="17" t="n"/>
-      <c r="L14" s="1" t="n"/>
+      <c r="L14" s="36" t="n"/>
       <c r="M14" s="17" t="n"/>
-      <c r="N14" s="1" t="n"/>
+      <c r="N14" s="36" t="n"/>
       <c r="O14" s="17" t="n"/>
-      <c r="P14" s="1" t="n"/>
-      <c r="Q14" s="1" t="n"/>
+      <c r="P14" s="35" t="n"/>
+      <c r="Q14" s="36" t="n"/>
       <c r="R14" s="17" t="n"/>
-      <c r="S14" s="1" t="n"/>
-      <c r="T14" s="1" t="n"/>
+      <c r="S14" s="35" t="n"/>
+      <c r="T14" s="36" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="17" t="n">
         <v>4</v>
       </c>
       <c r="B15" s="17" t="n"/>
-      <c r="C15" s="1" t="n"/>
-      <c r="D15" s="1" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="36" t="n"/>
       <c r="E15" s="17" t="n"/>
-      <c r="F15" s="1" t="n"/>
-      <c r="G15" s="1" t="n"/>
+      <c r="F15" s="35" t="n"/>
+      <c r="G15" s="36" t="n"/>
       <c r="H15" s="17" t="n"/>
-      <c r="I15" s="1" t="n"/>
-      <c r="J15" s="1" t="n"/>
+      <c r="I15" s="35" t="n"/>
+      <c r="J15" s="36" t="n"/>
       <c r="K15" s="17" t="n"/>
-      <c r="L15" s="1" t="n"/>
+      <c r="L15" s="36" t="n"/>
       <c r="M15" s="17" t="n"/>
-      <c r="N15" s="1" t="n"/>
+      <c r="N15" s="36" t="n"/>
       <c r="O15" s="17" t="n"/>
-      <c r="P15" s="1" t="n"/>
-      <c r="Q15" s="1" t="n"/>
+      <c r="P15" s="35" t="n"/>
+      <c r="Q15" s="36" t="n"/>
       <c r="R15" s="17" t="n"/>
-      <c r="S15" s="1" t="n"/>
-      <c r="T15" s="1" t="n"/>
+      <c r="S15" s="35" t="n"/>
+      <c r="T15" s="36" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="17" t="n">
         <v>5</v>
       </c>
       <c r="B16" s="17" t="n"/>
-      <c r="C16" s="1" t="n"/>
-      <c r="D16" s="1" t="n"/>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="36" t="n"/>
       <c r="E16" s="17" t="n"/>
-      <c r="F16" s="1" t="n"/>
-      <c r="G16" s="1" t="n"/>
+      <c r="F16" s="35" t="n"/>
+      <c r="G16" s="36" t="n"/>
       <c r="H16" s="17" t="n"/>
-      <c r="I16" s="1" t="n"/>
-      <c r="J16" s="1" t="n"/>
+      <c r="I16" s="35" t="n"/>
+      <c r="J16" s="36" t="n"/>
       <c r="K16" s="17" t="n"/>
-      <c r="L16" s="1" t="n"/>
+      <c r="L16" s="36" t="n"/>
       <c r="M16" s="17" t="n"/>
-      <c r="N16" s="1" t="n"/>
+      <c r="N16" s="36" t="n"/>
       <c r="O16" s="17" t="n"/>
-      <c r="P16" s="1" t="n"/>
-      <c r="Q16" s="1" t="n"/>
+      <c r="P16" s="35" t="n"/>
+      <c r="Q16" s="36" t="n"/>
       <c r="R16" s="17" t="n"/>
-      <c r="S16" s="1" t="n"/>
-      <c r="T16" s="1" t="n"/>
+      <c r="S16" s="35" t="n"/>
+      <c r="T16" s="36" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="17" t="n">
         <v>6</v>
       </c>
       <c r="B17" s="17" t="n"/>
-      <c r="C17" s="1" t="n"/>
-      <c r="D17" s="1" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="36" t="n"/>
       <c r="E17" s="17" t="n"/>
-      <c r="F17" s="1" t="n"/>
-      <c r="G17" s="1" t="n"/>
+      <c r="F17" s="35" t="n"/>
+      <c r="G17" s="36" t="n"/>
       <c r="H17" s="17" t="n"/>
-      <c r="I17" s="1" t="n"/>
-      <c r="J17" s="1" t="n"/>
+      <c r="I17" s="35" t="n"/>
+      <c r="J17" s="36" t="n"/>
       <c r="K17" s="17" t="n"/>
-      <c r="L17" s="1" t="n"/>
+      <c r="L17" s="36" t="n"/>
       <c r="M17" s="17" t="n"/>
-      <c r="N17" s="1" t="n"/>
+      <c r="N17" s="36" t="n"/>
       <c r="O17" s="17" t="n"/>
-      <c r="P17" s="1" t="n"/>
-      <c r="Q17" s="1" t="n"/>
+      <c r="P17" s="35" t="n"/>
+      <c r="Q17" s="36" t="n"/>
       <c r="R17" s="17" t="n"/>
-      <c r="S17" s="1" t="n"/>
-      <c r="T17" s="1" t="n"/>
+      <c r="S17" s="35" t="n"/>
+      <c r="T17" s="36" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="17" t="n">
         <v>7</v>
       </c>
       <c r="B18" s="17" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="36" t="n"/>
       <c r="E18" s="17" t="n"/>
-      <c r="F18" s="1" t="n"/>
-      <c r="G18" s="1" t="n"/>
+      <c r="F18" s="35" t="n"/>
+      <c r="G18" s="36" t="n"/>
       <c r="H18" s="17" t="n"/>
-      <c r="I18" s="1" t="n"/>
-      <c r="J18" s="1" t="n"/>
+      <c r="I18" s="35" t="n"/>
+      <c r="J18" s="36" t="n"/>
       <c r="K18" s="17" t="n"/>
-      <c r="L18" s="1" t="n"/>
+      <c r="L18" s="36" t="n"/>
       <c r="M18" s="17" t="n"/>
-      <c r="N18" s="1" t="n"/>
+      <c r="N18" s="36" t="n"/>
       <c r="O18" s="17" t="n"/>
-      <c r="P18" s="1" t="n"/>
-      <c r="Q18" s="1" t="n"/>
+      <c r="P18" s="35" t="n"/>
+      <c r="Q18" s="36" t="n"/>
       <c r="R18" s="17" t="n"/>
-      <c r="S18" s="1" t="n"/>
-      <c r="T18" s="1" t="n"/>
+      <c r="S18" s="35" t="n"/>
+      <c r="T18" s="36" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="17" t="n">
         <v>8</v>
       </c>
       <c r="B19" s="17" t="n"/>
-      <c r="C19" s="1" t="n"/>
-      <c r="D19" s="1" t="n"/>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="36" t="n"/>
       <c r="E19" s="17" t="n"/>
-      <c r="F19" s="1" t="n"/>
-      <c r="G19" s="1" t="n"/>
+      <c r="F19" s="35" t="n"/>
+      <c r="G19" s="36" t="n"/>
       <c r="H19" s="17" t="n"/>
-      <c r="I19" s="1" t="n"/>
-      <c r="J19" s="1" t="n"/>
+      <c r="I19" s="35" t="n"/>
+      <c r="J19" s="36" t="n"/>
       <c r="K19" s="17" t="n"/>
-      <c r="L19" s="1" t="n"/>
+      <c r="L19" s="36" t="n"/>
       <c r="M19" s="17" t="n"/>
-      <c r="N19" s="1" t="n"/>
+      <c r="N19" s="36" t="n"/>
       <c r="O19" s="17" t="n"/>
-      <c r="P19" s="1" t="n"/>
-      <c r="Q19" s="1" t="n"/>
+      <c r="P19" s="35" t="n"/>
+      <c r="Q19" s="36" t="n"/>
       <c r="R19" s="17" t="n"/>
-      <c r="S19" s="1" t="n"/>
-      <c r="T19" s="1" t="n"/>
-    </row>
+      <c r="S19" s="35" t="n"/>
+      <c r="T19" s="36" t="n"/>
+    </row>
+    <row r="20"/>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>CHECKS BEFORE DISPATCH / الفحوصات قبل الإرسال</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="13" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="13" t="n"/>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="13" t="n"/>
-      <c r="L21" s="13" t="n"/>
-      <c r="M21" s="13" t="n"/>
-      <c r="N21" s="13" t="n"/>
-      <c r="O21" s="13" t="n"/>
-      <c r="P21" s="13" t="n"/>
-      <c r="Q21" s="13" t="n"/>
-      <c r="R21" s="13" t="n"/>
-      <c r="S21" s="13" t="n"/>
-      <c r="T21" s="13" t="n"/>
+      <c r="B21" s="35" t="n"/>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="35" t="n"/>
+      <c r="F21" s="35" t="n"/>
+      <c r="G21" s="35" t="n"/>
+      <c r="H21" s="35" t="n"/>
+      <c r="I21" s="35" t="n"/>
+      <c r="J21" s="35" t="n"/>
+      <c r="K21" s="35" t="n"/>
+      <c r="L21" s="35" t="n"/>
+      <c r="M21" s="35" t="n"/>
+      <c r="N21" s="35" t="n"/>
+      <c r="O21" s="35" t="n"/>
+      <c r="P21" s="35" t="n"/>
+      <c r="Q21" s="35" t="n"/>
+      <c r="R21" s="35" t="n"/>
+      <c r="S21" s="35" t="n"/>
+      <c r="T21" s="36" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="39" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Check item / بند الفحص</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="16" t="inlineStr">
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="35" t="n"/>
+      <c r="E22" s="35" t="n"/>
+      <c r="F22" s="35" t="n"/>
+      <c r="G22" s="35" t="n"/>
+      <c r="H22" s="35" t="n"/>
+      <c r="I22" s="35" t="n"/>
+      <c r="J22" s="35" t="n"/>
+      <c r="K22" s="35" t="n"/>
+      <c r="L22" s="35" t="n"/>
+      <c r="M22" s="35" t="n"/>
+      <c r="N22" s="36" t="n"/>
+      <c r="O22" s="38" t="inlineStr">
         <is>
           <t>Yes
 نعم</t>
         </is>
       </c>
-      <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="16" t="inlineStr">
+      <c r="P22" s="36" t="n"/>
+      <c r="Q22" s="38" t="inlineStr">
         <is>
           <t>No
 لا</t>
         </is>
       </c>
-      <c r="R22" s="5" t="n"/>
-      <c r="S22" s="16" t="inlineStr">
+      <c r="R22" s="36" t="n"/>
+      <c r="S22" s="38" t="inlineStr">
         <is>
           <t>N/A
 لا ينطبق</t>
         </is>
       </c>
-      <c r="T22" s="5" t="n"/>
+      <c r="T22" s="36" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="19" t="n">
@@ -1249,36 +1408,36 @@
 الكراتين وقائمة التعبئة موسومة بالادعاء العضوي ورقم الطلب.</t>
         </is>
       </c>
-      <c r="C23" s="1" t="n"/>
-      <c r="D23" s="1" t="n"/>
-      <c r="E23" s="1" t="n"/>
-      <c r="F23" s="1" t="n"/>
-      <c r="G23" s="1" t="n"/>
-      <c r="H23" s="1" t="n"/>
-      <c r="I23" s="1" t="n"/>
-      <c r="J23" s="1" t="n"/>
-      <c r="K23" s="1" t="n"/>
-      <c r="L23" s="1" t="n"/>
-      <c r="M23" s="1" t="n"/>
-      <c r="N23" s="1" t="n"/>
+      <c r="C23" s="35" t="n"/>
+      <c r="D23" s="35" t="n"/>
+      <c r="E23" s="35" t="n"/>
+      <c r="F23" s="35" t="n"/>
+      <c r="G23" s="35" t="n"/>
+      <c r="H23" s="35" t="n"/>
+      <c r="I23" s="35" t="n"/>
+      <c r="J23" s="35" t="n"/>
+      <c r="K23" s="35" t="n"/>
+      <c r="L23" s="35" t="n"/>
+      <c r="M23" s="35" t="n"/>
+      <c r="N23" s="36" t="n"/>
       <c r="O23" s="21" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="P23" s="1" t="n"/>
+      <c r="P23" s="36" t="n"/>
       <c r="Q23" s="21" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="R23" s="1" t="n"/>
+      <c r="R23" s="36" t="n"/>
       <c r="S23" s="21" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="T23" s="1" t="n"/>
+      <c r="T23" s="36" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="19" t="n">
@@ -1290,36 +1449,36 @@
 ملصقات المنتج تطابق التصميم المعتمد وموافقة جهة الاعتماد.</t>
         </is>
       </c>
-      <c r="C24" s="1" t="n"/>
-      <c r="D24" s="1" t="n"/>
-      <c r="E24" s="1" t="n"/>
-      <c r="F24" s="1" t="n"/>
-      <c r="G24" s="1" t="n"/>
-      <c r="H24" s="1" t="n"/>
-      <c r="I24" s="1" t="n"/>
-      <c r="J24" s="1" t="n"/>
-      <c r="K24" s="1" t="n"/>
-      <c r="L24" s="1" t="n"/>
-      <c r="M24" s="1" t="n"/>
-      <c r="N24" s="1" t="n"/>
+      <c r="C24" s="35" t="n"/>
+      <c r="D24" s="35" t="n"/>
+      <c r="E24" s="35" t="n"/>
+      <c r="F24" s="35" t="n"/>
+      <c r="G24" s="35" t="n"/>
+      <c r="H24" s="35" t="n"/>
+      <c r="I24" s="35" t="n"/>
+      <c r="J24" s="35" t="n"/>
+      <c r="K24" s="35" t="n"/>
+      <c r="L24" s="35" t="n"/>
+      <c r="M24" s="35" t="n"/>
+      <c r="N24" s="36" t="n"/>
       <c r="O24" s="21" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="P24" s="1" t="n"/>
+      <c r="P24" s="36" t="n"/>
       <c r="Q24" s="21" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="R24" s="1" t="n"/>
+      <c r="R24" s="36" t="n"/>
       <c r="S24" s="21" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="T24" s="1" t="n"/>
+      <c r="T24" s="36" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="19" t="n">
@@ -1331,36 +1490,36 @@
 الفاتورة ووثائق التسليم تُظهر رقم الشهادة والادعاء العضوي.</t>
         </is>
       </c>
-      <c r="C25" s="1" t="n"/>
-      <c r="D25" s="1" t="n"/>
-      <c r="E25" s="1" t="n"/>
-      <c r="F25" s="1" t="n"/>
-      <c r="G25" s="1" t="n"/>
-      <c r="H25" s="1" t="n"/>
-      <c r="I25" s="1" t="n"/>
-      <c r="J25" s="1" t="n"/>
-      <c r="K25" s="1" t="n"/>
-      <c r="L25" s="1" t="n"/>
-      <c r="M25" s="1" t="n"/>
-      <c r="N25" s="1" t="n"/>
+      <c r="C25" s="35" t="n"/>
+      <c r="D25" s="35" t="n"/>
+      <c r="E25" s="35" t="n"/>
+      <c r="F25" s="35" t="n"/>
+      <c r="G25" s="35" t="n"/>
+      <c r="H25" s="35" t="n"/>
+      <c r="I25" s="35" t="n"/>
+      <c r="J25" s="35" t="n"/>
+      <c r="K25" s="35" t="n"/>
+      <c r="L25" s="35" t="n"/>
+      <c r="M25" s="35" t="n"/>
+      <c r="N25" s="36" t="n"/>
       <c r="O25" s="21" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="P25" s="1" t="n"/>
+      <c r="P25" s="36" t="n"/>
       <c r="Q25" s="21" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="R25" s="1" t="n"/>
+      <c r="R25" s="36" t="n"/>
       <c r="S25" s="21" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="T25" s="1" t="n"/>
+      <c r="T25" s="36" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="19" t="n">
@@ -1372,144 +1531,145 @@
 البضائع العضوية مفصولة عن التقليدية في المركبة أو معلّمة بوضوح.</t>
         </is>
       </c>
-      <c r="C26" s="1" t="n"/>
-      <c r="D26" s="1" t="n"/>
-      <c r="E26" s="1" t="n"/>
-      <c r="F26" s="1" t="n"/>
-      <c r="G26" s="1" t="n"/>
-      <c r="H26" s="1" t="n"/>
-      <c r="I26" s="1" t="n"/>
-      <c r="J26" s="1" t="n"/>
-      <c r="K26" s="1" t="n"/>
-      <c r="L26" s="1" t="n"/>
-      <c r="M26" s="1" t="n"/>
-      <c r="N26" s="1" t="n"/>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="35" t="n"/>
+      <c r="E26" s="35" t="n"/>
+      <c r="F26" s="35" t="n"/>
+      <c r="G26" s="35" t="n"/>
+      <c r="H26" s="35" t="n"/>
+      <c r="I26" s="35" t="n"/>
+      <c r="J26" s="35" t="n"/>
+      <c r="K26" s="35" t="n"/>
+      <c r="L26" s="35" t="n"/>
+      <c r="M26" s="35" t="n"/>
+      <c r="N26" s="36" t="n"/>
       <c r="O26" s="21" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="P26" s="1" t="n"/>
+      <c r="P26" s="36" t="n"/>
       <c r="Q26" s="21" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="R26" s="1" t="n"/>
+      <c r="R26" s="36" t="n"/>
       <c r="S26" s="21" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="T26" s="1" t="n"/>
-    </row>
+      <c r="T26" s="36" t="n"/>
+    </row>
+    <row r="27"/>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="34" t="inlineStr">
         <is>
           <t>TC REQUEST / طلب شهادة المعاملة</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n"/>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="13" t="n"/>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="13" t="n"/>
-      <c r="J28" s="13" t="n"/>
-      <c r="K28" s="13" t="n"/>
-      <c r="L28" s="13" t="n"/>
-      <c r="M28" s="13" t="n"/>
-      <c r="N28" s="13" t="n"/>
-      <c r="O28" s="13" t="n"/>
-      <c r="P28" s="13" t="n"/>
-      <c r="Q28" s="13" t="n"/>
-      <c r="R28" s="13" t="n"/>
-      <c r="S28" s="13" t="n"/>
-      <c r="T28" s="13" t="n"/>
+      <c r="B28" s="35" t="n"/>
+      <c r="C28" s="35" t="n"/>
+      <c r="D28" s="35" t="n"/>
+      <c r="E28" s="35" t="n"/>
+      <c r="F28" s="35" t="n"/>
+      <c r="G28" s="35" t="n"/>
+      <c r="H28" s="35" t="n"/>
+      <c r="I28" s="35" t="n"/>
+      <c r="J28" s="35" t="n"/>
+      <c r="K28" s="35" t="n"/>
+      <c r="L28" s="35" t="n"/>
+      <c r="M28" s="35" t="n"/>
+      <c r="N28" s="35" t="n"/>
+      <c r="O28" s="35" t="n"/>
+      <c r="P28" s="35" t="n"/>
+      <c r="Q28" s="35" t="n"/>
+      <c r="R28" s="35" t="n"/>
+      <c r="S28" s="35" t="n"/>
+      <c r="T28" s="36" t="n"/>
     </row>
     <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="37" t="inlineStr">
         <is>
           <t>Shipment data sent to certification body - date
 تاريخ إرسال بيانات الشحنة إلى جهة الاعتماد</t>
         </is>
       </c>
-      <c r="B29" s="15" t="n"/>
-      <c r="C29" s="15" t="n"/>
-      <c r="D29" s="15" t="n"/>
-      <c r="E29" s="15" t="n"/>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="B29" s="35" t="n"/>
+      <c r="C29" s="35" t="n"/>
+      <c r="D29" s="35" t="n"/>
+      <c r="E29" s="35" t="n"/>
+      <c r="F29" s="35" t="n"/>
+      <c r="G29" s="36" t="n"/>
+      <c r="H29" s="37" t="inlineStr">
         <is>
           <t>Request reference
 مرجع الطلب</t>
         </is>
       </c>
-      <c r="I29" s="15" t="n"/>
-      <c r="J29" s="15" t="n"/>
-      <c r="K29" s="15" t="n"/>
-      <c r="L29" s="15" t="n"/>
-      <c r="M29" s="15" t="n"/>
-      <c r="N29" s="14" t="inlineStr">
+      <c r="I29" s="35" t="n"/>
+      <c r="J29" s="35" t="n"/>
+      <c r="K29" s="35" t="n"/>
+      <c r="L29" s="35" t="n"/>
+      <c r="M29" s="36" t="n"/>
+      <c r="N29" s="37" t="inlineStr">
         <is>
           <t>TC No received / date
 رقم TC المستلم / التاريخ</t>
         </is>
       </c>
-      <c r="O29" s="15" t="n"/>
-      <c r="P29" s="15" t="n"/>
-      <c r="Q29" s="15" t="n"/>
-      <c r="R29" s="15" t="n"/>
-      <c r="S29" s="15" t="n"/>
-      <c r="T29" s="15" t="n"/>
+      <c r="O29" s="35" t="n"/>
+      <c r="P29" s="35" t="n"/>
+      <c r="Q29" s="35" t="n"/>
+      <c r="R29" s="35" t="n"/>
+      <c r="S29" s="35" t="n"/>
+      <c r="T29" s="36" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="39" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B30" s="18" t="inlineStr">
+      <c r="B30" s="39" t="inlineStr">
         <is>
           <t>Check item / بند الفحص</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="16" t="inlineStr">
+      <c r="C30" s="35" t="n"/>
+      <c r="D30" s="35" t="n"/>
+      <c r="E30" s="35" t="n"/>
+      <c r="F30" s="35" t="n"/>
+      <c r="G30" s="35" t="n"/>
+      <c r="H30" s="35" t="n"/>
+      <c r="I30" s="35" t="n"/>
+      <c r="J30" s="35" t="n"/>
+      <c r="K30" s="35" t="n"/>
+      <c r="L30" s="35" t="n"/>
+      <c r="M30" s="35" t="n"/>
+      <c r="N30" s="36" t="n"/>
+      <c r="O30" s="38" t="inlineStr">
         <is>
           <t>Yes
 نعم</t>
         </is>
       </c>
-      <c r="P30" s="5" t="n"/>
-      <c r="Q30" s="16" t="inlineStr">
+      <c r="P30" s="36" t="n"/>
+      <c r="Q30" s="38" t="inlineStr">
         <is>
           <t>No
 لا</t>
         </is>
       </c>
-      <c r="R30" s="5" t="n"/>
-      <c r="S30" s="16" t="inlineStr">
+      <c r="R30" s="36" t="n"/>
+      <c r="S30" s="38" t="inlineStr">
         <is>
           <t>N/A
 لا ينطبق</t>
         </is>
       </c>
-      <c r="T30" s="5" t="n"/>
+      <c r="T30" s="36" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="19" t="n">
@@ -1521,70 +1681,71 @@
 استُلمت شهادة المعاملة وطُوبقت مع الشحنة وحُفظت مع الفاتورة وقائمة التعبئة وبوليصة الشحن.</t>
         </is>
       </c>
-      <c r="C31" s="1" t="n"/>
-      <c r="D31" s="1" t="n"/>
-      <c r="E31" s="1" t="n"/>
-      <c r="F31" s="1" t="n"/>
-      <c r="G31" s="1" t="n"/>
-      <c r="H31" s="1" t="n"/>
-      <c r="I31" s="1" t="n"/>
-      <c r="J31" s="1" t="n"/>
-      <c r="K31" s="1" t="n"/>
-      <c r="L31" s="1" t="n"/>
-      <c r="M31" s="1" t="n"/>
-      <c r="N31" s="1" t="n"/>
+      <c r="C31" s="35" t="n"/>
+      <c r="D31" s="35" t="n"/>
+      <c r="E31" s="35" t="n"/>
+      <c r="F31" s="35" t="n"/>
+      <c r="G31" s="35" t="n"/>
+      <c r="H31" s="35" t="n"/>
+      <c r="I31" s="35" t="n"/>
+      <c r="J31" s="35" t="n"/>
+      <c r="K31" s="35" t="n"/>
+      <c r="L31" s="35" t="n"/>
+      <c r="M31" s="35" t="n"/>
+      <c r="N31" s="36" t="n"/>
       <c r="O31" s="21" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="P31" s="1" t="n"/>
+      <c r="P31" s="36" t="n"/>
       <c r="Q31" s="21" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="R31" s="1" t="n"/>
+      <c r="R31" s="36" t="n"/>
       <c r="S31" s="21" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="T31" s="1" t="n"/>
-    </row>
+      <c r="T31" s="36" t="n"/>
+    </row>
+    <row r="32"/>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="40" t="inlineStr">
         <is>
           <t>Shipping / الشحن</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="B33" s="41" t="n"/>
+      <c r="C33" s="41" t="n"/>
+      <c r="D33" s="41" t="n"/>
+      <c r="E33" s="41" t="n"/>
+      <c r="F33" s="41" t="n"/>
+      <c r="G33" s="42" t="n"/>
+      <c r="H33" s="40" t="inlineStr">
         <is>
           <t>OCS / GOTS Coordinator / منسق OCS / GOTS</t>
         </is>
       </c>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="n"/>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="n"/>
-      <c r="O33" s="16" t="inlineStr">
+      <c r="I33" s="41" t="n"/>
+      <c r="J33" s="41" t="n"/>
+      <c r="K33" s="41" t="n"/>
+      <c r="L33" s="41" t="n"/>
+      <c r="M33" s="41" t="n"/>
+      <c r="N33" s="42" t="n"/>
+      <c r="O33" s="40" t="inlineStr">
         <is>
           <t>Quality / الجودة</t>
         </is>
       </c>
-      <c r="P33" s="5" t="n"/>
-      <c r="Q33" s="5" t="n"/>
-      <c r="R33" s="5" t="n"/>
-      <c r="S33" s="5" t="n"/>
-      <c r="T33" s="5" t="n"/>
+      <c r="P33" s="41" t="n"/>
+      <c r="Q33" s="41" t="n"/>
+      <c r="R33" s="41" t="n"/>
+      <c r="S33" s="41" t="n"/>
+      <c r="T33" s="42" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="22" t="inlineStr">
@@ -1592,106 +1753,93 @@
           <t>Name - Signature - Date / الاسم - التوقيع - التاريخ</t>
         </is>
       </c>
-      <c r="B34" s="1" t="n"/>
-      <c r="C34" s="1" t="n"/>
-      <c r="D34" s="1" t="n"/>
-      <c r="E34" s="1" t="n"/>
-      <c r="F34" s="1" t="n"/>
-      <c r="G34" s="1" t="n"/>
+      <c r="B34" s="43" t="n"/>
+      <c r="C34" s="43" t="n"/>
+      <c r="D34" s="43" t="n"/>
+      <c r="E34" s="43" t="n"/>
+      <c r="F34" s="43" t="n"/>
+      <c r="G34" s="2" t="n"/>
       <c r="H34" s="22" t="inlineStr">
         <is>
           <t>Name - Signature - Date / الاسم - التوقيع - التاريخ</t>
         </is>
       </c>
-      <c r="I34" s="1" t="n"/>
-      <c r="J34" s="1" t="n"/>
-      <c r="K34" s="1" t="n"/>
-      <c r="L34" s="1" t="n"/>
-      <c r="M34" s="1" t="n"/>
-      <c r="N34" s="1" t="n"/>
+      <c r="I34" s="43" t="n"/>
+      <c r="J34" s="43" t="n"/>
+      <c r="K34" s="43" t="n"/>
+      <c r="L34" s="43" t="n"/>
+      <c r="M34" s="43" t="n"/>
+      <c r="N34" s="2" t="n"/>
       <c r="O34" s="22" t="inlineStr">
         <is>
           <t>Name - Signature - Date / الاسم - التوقيع - التاريخ</t>
         </is>
       </c>
-      <c r="P34" s="1" t="n"/>
-      <c r="Q34" s="1" t="n"/>
-      <c r="R34" s="1" t="n"/>
-      <c r="S34" s="1" t="n"/>
-      <c r="T34" s="1" t="n"/>
+      <c r="P34" s="43" t="n"/>
+      <c r="Q34" s="43" t="n"/>
+      <c r="R34" s="43" t="n"/>
+      <c r="S34" s="43" t="n"/>
+      <c r="T34" s="2" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n"/>
-      <c r="B35" s="1" t="n"/>
-      <c r="C35" s="1" t="n"/>
-      <c r="D35" s="1" t="n"/>
-      <c r="E35" s="1" t="n"/>
-      <c r="F35" s="1" t="n"/>
-      <c r="G35" s="1" t="n"/>
-      <c r="H35" s="1" t="n"/>
-      <c r="I35" s="1" t="n"/>
-      <c r="J35" s="1" t="n"/>
-      <c r="K35" s="1" t="n"/>
-      <c r="L35" s="1" t="n"/>
-      <c r="M35" s="1" t="n"/>
-      <c r="N35" s="1" t="n"/>
-      <c r="O35" s="1" t="n"/>
-      <c r="P35" s="1" t="n"/>
-      <c r="Q35" s="1" t="n"/>
-      <c r="R35" s="1" t="n"/>
-      <c r="S35" s="1" t="n"/>
-      <c r="T35" s="1" t="n"/>
+      <c r="A35" s="7" t="n"/>
+      <c r="G35" s="8" t="n"/>
+      <c r="H35" s="7" t="n"/>
+      <c r="N35" s="8" t="n"/>
+      <c r="O35" s="7" t="n"/>
+      <c r="T35" s="8" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n"/>
-      <c r="B36" s="1" t="n"/>
-      <c r="C36" s="1" t="n"/>
-      <c r="D36" s="1" t="n"/>
-      <c r="E36" s="1" t="n"/>
-      <c r="F36" s="1" t="n"/>
-      <c r="G36" s="1" t="n"/>
-      <c r="H36" s="1" t="n"/>
-      <c r="I36" s="1" t="n"/>
-      <c r="J36" s="1" t="n"/>
-      <c r="K36" s="1" t="n"/>
-      <c r="L36" s="1" t="n"/>
-      <c r="M36" s="1" t="n"/>
-      <c r="N36" s="1" t="n"/>
-      <c r="O36" s="1" t="n"/>
-      <c r="P36" s="1" t="n"/>
-      <c r="Q36" s="1" t="n"/>
-      <c r="R36" s="1" t="n"/>
-      <c r="S36" s="1" t="n"/>
-      <c r="T36" s="1" t="n"/>
-    </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="23" t="inlineStr">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="44" t="n"/>
+      <c r="C36" s="44" t="n"/>
+      <c r="D36" s="44" t="n"/>
+      <c r="E36" s="44" t="n"/>
+      <c r="F36" s="44" t="n"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="10" t="n"/>
+      <c r="I36" s="44" t="n"/>
+      <c r="J36" s="44" t="n"/>
+      <c r="K36" s="44" t="n"/>
+      <c r="L36" s="44" t="n"/>
+      <c r="M36" s="44" t="n"/>
+      <c r="N36" s="11" t="n"/>
+      <c r="O36" s="10" t="n"/>
+      <c r="P36" s="44" t="n"/>
+      <c r="Q36" s="44" t="n"/>
+      <c r="R36" s="44" t="n"/>
+      <c r="S36" s="44" t="n"/>
+      <c r="T36" s="11" t="n"/>
+    </row>
+    <row r="37"/>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="34" t="inlineStr">
         <is>
           <t>Retention: at least 5 years or per certification body / customer requirement. Any nonconformity opens a corrective action (DÖF). | الاحتفاظ: 5 سنوات على الأقل أو حسب متطلبات جهة الاعتماد / العميل. وتفتح أي حالة عدم مطابقة إجراءً تصحيحيًا (DÖF).</t>
         </is>
       </c>
-      <c r="B38" s="1" t="n"/>
-      <c r="C38" s="1" t="n"/>
-      <c r="D38" s="1" t="n"/>
-      <c r="E38" s="1" t="n"/>
-      <c r="F38" s="1" t="n"/>
-      <c r="G38" s="1" t="n"/>
-      <c r="H38" s="1" t="n"/>
-      <c r="I38" s="1" t="n"/>
-      <c r="J38" s="1" t="n"/>
-      <c r="K38" s="1" t="n"/>
-      <c r="L38" s="1" t="n"/>
-      <c r="M38" s="1" t="n"/>
-      <c r="N38" s="1" t="n"/>
-      <c r="O38" s="1" t="n"/>
-      <c r="P38" s="1" t="n"/>
-      <c r="Q38" s="1" t="n"/>
-      <c r="R38" s="1" t="n"/>
-      <c r="S38" s="1" t="n"/>
-      <c r="T38" s="1" t="n"/>
+      <c r="B38" s="41" t="n"/>
+      <c r="C38" s="41" t="n"/>
+      <c r="D38" s="41" t="n"/>
+      <c r="E38" s="41" t="n"/>
+      <c r="F38" s="41" t="n"/>
+      <c r="G38" s="41" t="n"/>
+      <c r="H38" s="41" t="n"/>
+      <c r="I38" s="41" t="n"/>
+      <c r="J38" s="41" t="n"/>
+      <c r="K38" s="41" t="n"/>
+      <c r="L38" s="41" t="n"/>
+      <c r="M38" s="41" t="n"/>
+      <c r="N38" s="41" t="n"/>
+      <c r="O38" s="41" t="n"/>
+      <c r="P38" s="41" t="n"/>
+      <c r="Q38" s="41" t="n"/>
+      <c r="R38" s="41" t="n"/>
+      <c r="S38" s="41" t="n"/>
+      <c r="T38" s="42" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="119">
+  <mergeCells count="117">
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="H17:J17"/>
@@ -1720,11 +1868,11 @@
     <mergeCell ref="A28:T28"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="S22:T22"/>
-    <mergeCell ref="C1:Q1"/>
     <mergeCell ref="K15:L15"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="B19:D19"/>
+    <mergeCell ref="D1:O4"/>
     <mergeCell ref="Q23:R23"/>
     <mergeCell ref="O12:Q12"/>
     <mergeCell ref="R17:T17"/>
@@ -1768,7 +1916,6 @@
     <mergeCell ref="M15:N15"/>
     <mergeCell ref="H18:J18"/>
     <mergeCell ref="M12:N12"/>
-    <mergeCell ref="C1:Q4"/>
     <mergeCell ref="P7:T7"/>
     <mergeCell ref="A21:T21"/>
     <mergeCell ref="E12:G12"/>
@@ -1776,7 +1923,6 @@
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="R19:T19"/>
     <mergeCell ref="O23:P23"/>
-    <mergeCell ref="A1:B4"/>
     <mergeCell ref="S26:T26"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="O34:T36"/>

--- a/formlar/16. Organik Üretim/EMS.OR.FRM.21.07. Organik Sevkiyat ve TC Talep Formu.xlsx
+++ b/formlar/16. Organik Üretim/EMS.OR.FRM.21.07. Organik Sevkiyat ve TC Talep Formu.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -96,6 +96,12 @@
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -130,7 +136,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -262,11 +268,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -360,6 +394,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,6 +503,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -494,6 +536,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -819,23 +864,24 @@
       <c r="A1" s="24" t="n"/>
       <c r="B1" s="25" t="n"/>
       <c r="C1" s="26" t="n"/>
-      <c r="D1" s="27" t="inlineStr">
-        <is>
-          <t>ORGANIC SHIPMENT AND TC REQUEST FORM
+      <c r="D1" s="45" t="inlineStr">
+        <is>
+          <t>ORGANİK SEVKİYAT VE TC TALEP FORMU
+ORGANIC SHIPMENT AND TC REQUEST FORM
 نموذج الشحن العضوي وطلب شهادة المعاملة</t>
         </is>
       </c>
-      <c r="E1" s="25" t="n"/>
-      <c r="F1" s="25" t="n"/>
-      <c r="G1" s="25" t="n"/>
-      <c r="H1" s="25" t="n"/>
-      <c r="I1" s="25" t="n"/>
-      <c r="J1" s="25" t="n"/>
-      <c r="K1" s="25" t="n"/>
-      <c r="L1" s="25" t="n"/>
-      <c r="M1" s="25" t="n"/>
-      <c r="N1" s="25" t="n"/>
-      <c r="O1" s="25" t="n"/>
+      <c r="E1" s="46" t="n"/>
+      <c r="F1" s="46" t="n"/>
+      <c r="G1" s="46" t="n"/>
+      <c r="H1" s="46" t="n"/>
+      <c r="I1" s="46" t="n"/>
+      <c r="J1" s="46" t="n"/>
+      <c r="K1" s="46" t="n"/>
+      <c r="L1" s="46" t="n"/>
+      <c r="M1" s="46" t="n"/>
+      <c r="N1" s="46" t="n"/>
+      <c r="O1" s="46" t="n"/>
       <c r="P1" s="25" t="n"/>
       <c r="Q1" s="25" t="n"/>
       <c r="R1" s="28" t="inlineStr">
@@ -843,7 +889,7 @@
           <t>DATE / التاريخ</t>
         </is>
       </c>
-      <c r="S1" s="29" t="n"/>
+      <c r="S1" s="47" t="n"/>
       <c r="T1" s="30" t="inlineStr">
         <is>
           <t>….../….../.…</t>
@@ -854,18 +900,6 @@
       <c r="A2" s="31" t="n"/>
       <c r="B2" s="32" t="n"/>
       <c r="C2" s="32" t="n"/>
-      <c r="D2" s="32" t="n"/>
-      <c r="E2" s="32" t="n"/>
-      <c r="F2" s="32" t="n"/>
-      <c r="G2" s="32" t="n"/>
-      <c r="H2" s="32" t="n"/>
-      <c r="I2" s="32" t="n"/>
-      <c r="J2" s="32" t="n"/>
-      <c r="K2" s="32" t="n"/>
-      <c r="L2" s="32" t="n"/>
-      <c r="M2" s="32" t="n"/>
-      <c r="N2" s="32" t="n"/>
-      <c r="O2" s="32" t="n"/>
       <c r="P2" s="32" t="n"/>
       <c r="Q2" s="32" t="n"/>
       <c r="R2" s="28" t="inlineStr">
@@ -873,7 +907,7 @@
           <t>FORM NUMBER / رقم النموذج</t>
         </is>
       </c>
-      <c r="S2" s="29" t="n"/>
+      <c r="S2" s="47" t="n"/>
       <c r="T2" s="33" t="inlineStr">
         <is>
           <t>EMS.OR.FRM.21.07</t>
@@ -884,18 +918,6 @@
       <c r="A3" s="31" t="n"/>
       <c r="B3" s="32" t="n"/>
       <c r="C3" s="32" t="n"/>
-      <c r="D3" s="32" t="n"/>
-      <c r="E3" s="32" t="n"/>
-      <c r="F3" s="32" t="n"/>
-      <c r="G3" s="32" t="n"/>
-      <c r="H3" s="32" t="n"/>
-      <c r="I3" s="32" t="n"/>
-      <c r="J3" s="32" t="n"/>
-      <c r="K3" s="32" t="n"/>
-      <c r="L3" s="32" t="n"/>
-      <c r="M3" s="32" t="n"/>
-      <c r="N3" s="32" t="n"/>
-      <c r="O3" s="32" t="n"/>
       <c r="P3" s="32" t="n"/>
       <c r="Q3" s="32" t="n"/>
       <c r="R3" s="28" t="inlineStr">
@@ -903,7 +925,7 @@
           <t>REVISION / المراجعة</t>
         </is>
       </c>
-      <c r="S3" s="29" t="n"/>
+      <c r="S3" s="47" t="n"/>
       <c r="T3" s="30" t="inlineStr">
         <is>
           <t>R00</t>
@@ -914,18 +936,6 @@
       <c r="A4" s="31" t="n"/>
       <c r="B4" s="32" t="n"/>
       <c r="C4" s="32" t="n"/>
-      <c r="D4" s="32" t="n"/>
-      <c r="E4" s="32" t="n"/>
-      <c r="F4" s="32" t="n"/>
-      <c r="G4" s="32" t="n"/>
-      <c r="H4" s="32" t="n"/>
-      <c r="I4" s="32" t="n"/>
-      <c r="J4" s="32" t="n"/>
-      <c r="K4" s="32" t="n"/>
-      <c r="L4" s="32" t="n"/>
-      <c r="M4" s="32" t="n"/>
-      <c r="N4" s="32" t="n"/>
-      <c r="O4" s="32" t="n"/>
       <c r="P4" s="32" t="n"/>
       <c r="Q4" s="32" t="n"/>
       <c r="R4" s="28" t="inlineStr">
@@ -933,14 +943,13 @@
           <t>PUBLIC. DATE / تاريخ النشر</t>
         </is>
       </c>
-      <c r="S4" s="29" t="n"/>
+      <c r="S4" s="47" t="n"/>
       <c r="T4" s="30" t="inlineStr">
         <is>
           <t>19.10.2026</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="34" t="inlineStr">
         <is>
@@ -1046,7 +1055,6 @@
       <c r="S8" s="35" t="n"/>
       <c r="T8" s="36" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="34" t="inlineStr">
         <is>
@@ -1326,7 +1334,6 @@
       <c r="S19" s="35" t="n"/>
       <c r="T19" s="36" t="n"/>
     </row>
-    <row r="20"/>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="34" t="inlineStr">
         <is>
@@ -1562,7 +1569,6 @@
       </c>
       <c r="T26" s="36" t="n"/>
     </row>
-    <row r="27"/>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="34" t="inlineStr">
         <is>
@@ -1712,40 +1718,39 @@
       </c>
       <c r="T31" s="36" t="n"/>
     </row>
-    <row r="32"/>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="40" t="inlineStr">
         <is>
           <t>Shipping / الشحن</t>
         </is>
       </c>
-      <c r="B33" s="41" t="n"/>
-      <c r="C33" s="41" t="n"/>
-      <c r="D33" s="41" t="n"/>
-      <c r="E33" s="41" t="n"/>
-      <c r="F33" s="41" t="n"/>
-      <c r="G33" s="42" t="n"/>
+      <c r="B33" s="35" t="n"/>
+      <c r="C33" s="35" t="n"/>
+      <c r="D33" s="35" t="n"/>
+      <c r="E33" s="35" t="n"/>
+      <c r="F33" s="35" t="n"/>
+      <c r="G33" s="36" t="n"/>
       <c r="H33" s="40" t="inlineStr">
         <is>
           <t>OCS / GOTS Coordinator / منسق OCS / GOTS</t>
         </is>
       </c>
-      <c r="I33" s="41" t="n"/>
-      <c r="J33" s="41" t="n"/>
-      <c r="K33" s="41" t="n"/>
-      <c r="L33" s="41" t="n"/>
-      <c r="M33" s="41" t="n"/>
-      <c r="N33" s="42" t="n"/>
+      <c r="I33" s="35" t="n"/>
+      <c r="J33" s="35" t="n"/>
+      <c r="K33" s="35" t="n"/>
+      <c r="L33" s="35" t="n"/>
+      <c r="M33" s="35" t="n"/>
+      <c r="N33" s="36" t="n"/>
       <c r="O33" s="40" t="inlineStr">
         <is>
           <t>Quality / الجودة</t>
         </is>
       </c>
-      <c r="P33" s="41" t="n"/>
-      <c r="Q33" s="41" t="n"/>
-      <c r="R33" s="41" t="n"/>
-      <c r="S33" s="41" t="n"/>
-      <c r="T33" s="42" t="n"/>
+      <c r="P33" s="35" t="n"/>
+      <c r="Q33" s="35" t="n"/>
+      <c r="R33" s="35" t="n"/>
+      <c r="S33" s="35" t="n"/>
+      <c r="T33" s="36" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="22" t="inlineStr">
@@ -1811,32 +1816,31 @@
       <c r="S36" s="44" t="n"/>
       <c r="T36" s="11" t="n"/>
     </row>
-    <row r="37"/>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="34" t="inlineStr">
         <is>
           <t>Retention: at least 5 years or per certification body / customer requirement. Any nonconformity opens a corrective action (DÖF). | الاحتفاظ: 5 سنوات على الأقل أو حسب متطلبات جهة الاعتماد / العميل. وتفتح أي حالة عدم مطابقة إجراءً تصحيحيًا (DÖF).</t>
         </is>
       </c>
-      <c r="B38" s="41" t="n"/>
-      <c r="C38" s="41" t="n"/>
-      <c r="D38" s="41" t="n"/>
-      <c r="E38" s="41" t="n"/>
-      <c r="F38" s="41" t="n"/>
-      <c r="G38" s="41" t="n"/>
-      <c r="H38" s="41" t="n"/>
-      <c r="I38" s="41" t="n"/>
-      <c r="J38" s="41" t="n"/>
-      <c r="K38" s="41" t="n"/>
-      <c r="L38" s="41" t="n"/>
-      <c r="M38" s="41" t="n"/>
-      <c r="N38" s="41" t="n"/>
-      <c r="O38" s="41" t="n"/>
-      <c r="P38" s="41" t="n"/>
-      <c r="Q38" s="41" t="n"/>
-      <c r="R38" s="41" t="n"/>
-      <c r="S38" s="41" t="n"/>
-      <c r="T38" s="42" t="n"/>
+      <c r="B38" s="35" t="n"/>
+      <c r="C38" s="35" t="n"/>
+      <c r="D38" s="35" t="n"/>
+      <c r="E38" s="35" t="n"/>
+      <c r="F38" s="35" t="n"/>
+      <c r="G38" s="35" t="n"/>
+      <c r="H38" s="35" t="n"/>
+      <c r="I38" s="35" t="n"/>
+      <c r="J38" s="35" t="n"/>
+      <c r="K38" s="35" t="n"/>
+      <c r="L38" s="35" t="n"/>
+      <c r="M38" s="35" t="n"/>
+      <c r="N38" s="35" t="n"/>
+      <c r="O38" s="35" t="n"/>
+      <c r="P38" s="35" t="n"/>
+      <c r="Q38" s="35" t="n"/>
+      <c r="R38" s="35" t="n"/>
+      <c r="S38" s="35" t="n"/>
+      <c r="T38" s="36" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="117">
